--- a/business-libraries/templates/三库填写模板_v4.xlsx
+++ b/business-libraries/templates/三库填写模板_v4.xlsx
@@ -25,6 +25,7 @@
     <sheet name="⑧ 工具-禁忌规则" sheetId="20" r:id="rId20"/>
     <sheet name="⑨ 关键词-路由" sheetId="21" r:id="rId21"/>
     <sheet name="⑩ 方案输出模板" sheetId="22" r:id="rId22"/>
+    <sheet name="⑪ 全链路推演算例" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -1052,12 +1053,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
-    <col min="4" max="4" width="51.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,228 +1086,228 @@
         <v>题[q1] &gt;= 4</v>
       </c>
       <c r="D2" t="str">
-        <v>反向计分题已自动折算后再取值</v>
+        <v>取的是折算后的分，不是教师点的那个选项——反向题看下面一行</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>某个维度的得分</v>
+        <v>【反向题的方向别写反】</v>
       </c>
       <c r="B3" t="str">
-        <v>维度[维度编码]</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>维度[EMOTION] &gt;= 4</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>维度编码取自 ④c，不是维度名称</v>
+        <v>这是最容易出错、且没有任何校验能拦住的一处</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>所有题目的总分</v>
+        <v xml:space="preserve">  正向题（问题越严重分越高）</v>
       </c>
       <c r="B4" t="str">
-        <v>总分</v>
+        <v>题[q1] &gt;= 4</v>
       </c>
       <c r="C4" t="str">
-        <v>总分 &gt;= 20</v>
+        <v>「身心疲惫」答 4/5 分 → 题[q1] = 4/5</v>
       </c>
       <c r="D4" t="str">
-        <v>反向计分题已折算</v>
+        <v>q1 反向计分=否。题[q1] &gt;= 4 就是「疲惫程度高」，符合直觉</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>所有题目的均分</v>
+        <v xml:space="preserve">  反向题（状态越好分越高）</v>
       </c>
       <c r="B5" t="str">
-        <v>均分</v>
+        <v>题[q3] &gt;= 4</v>
       </c>
       <c r="C5" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>「当班主任值得」答 1 分 → 题[q3] = 5</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>q3 反向计分=是，系统按 最小值+最大值−原始分 折算。所以 题[q3] &gt;= 4 表示「意义感低」，不是「意义感高」。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>最主导的维度</v>
+        <v xml:space="preserve">  写反了会怎样</v>
       </c>
       <c r="B6" t="str">
-        <v>TOP_DIM()</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>TOP_DIM() == 'EMOTION'</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>返回得分最高的维度编码</v>
+        <v>表达式合法、题号也存在，导入校验全部通过——但红线会打在状态好的教师身上，或者对真正高危的人永不触发。填完请对照 ④ 的「反向计分」列逐条确认方向。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>最薄弱的维度</v>
+        <v>某个维度的得分</v>
       </c>
       <c r="B7" t="str">
-        <v>BOTTOM_DIM()</v>
+        <v>维度[维度编码]</v>
       </c>
       <c r="C7" t="str">
-        <v>BOTTOM_DIM() == 'MEANING'</v>
+        <v>维度[EMOTION] &gt;= 4</v>
       </c>
       <c r="D7" t="str">
-        <v>返回得分最低的维度编码</v>
+        <v>维度编码取自 ④c，不是维度名称</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>某道题的原始作答值</v>
+        <v>所有题目的总分</v>
       </c>
       <c r="B8" t="str">
-        <v>原始[题号]</v>
+        <v>总分</v>
       </c>
       <c r="C8" t="str">
-        <v>原始[q3] == 1</v>
+        <v>总分 &gt;= 20</v>
       </c>
       <c r="D8" t="str">
-        <v>不做反向折算，一般不用</v>
+        <v>反向计分题已折算</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>并且 / 或者</v>
+        <v>所有题目的均分</v>
       </c>
       <c r="B9" t="str">
-        <v>且 / 或</v>
+        <v>均分</v>
       </c>
       <c r="C9" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &lt;= 2</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="D9" t="str">
-        <v>也可以写 &amp;&amp; ||，或英文 AND / OR</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>相等 / 不等</v>
+        <v>最主导的维度</v>
       </c>
       <c r="B10" t="str">
-        <v>== / !=</v>
+        <v>TOP_DIM()</v>
       </c>
       <c r="C10" t="str">
-        <v>题[q1] == 5</v>
+        <v>TOP_DIM() == 'EMOTION'</v>
       </c>
       <c r="D10" t="str">
-        <v>写单个 = 系统会自动当成 ==，但建议直接写 ==</v>
+        <v>返回得分最高的维度编码</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>自定义变量</v>
+        <v>最薄弱的维度</v>
       </c>
       <c r="B11" t="str">
-        <v>直接写变量名</v>
+        <v>BOTTOM_DIM()</v>
       </c>
       <c r="C11" t="str">
-        <v>情绪均分 &gt;= 4</v>
+        <v>BOTTOM_DIM() == 'MEANING'</v>
       </c>
       <c r="D11" t="str">
-        <v>变量在 ⑤b 里定义</v>
+        <v>返回得分最低的维度编码</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>某道题的原始作答值</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>原始[题号]</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>原始[q3] == 1</v>
       </c>
       <c r="D12" t="str">
-        <v>注意：条件里不支持加减乘除。需要算差值、比值，请在 ⑤b 里定义变量，或拆成两个条件用「且」连接。</v>
+        <v>不做反向折算，一般不用</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>并且 / 或者</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>且 / 或</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>题[q1] &gt;= 4 且 题[q3] &lt;= 2</v>
       </c>
       <c r="D13" t="str">
-        <v>变量名不要包含「且」「或」「总分」「均分」「主导维度」「短板维度」这些关键词，否则会被切坏。</v>
+        <v>也可以写 &amp;&amp; ||，或英文 AND / OR</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>相等 / 不等</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>== / !=</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>题[q1] == 5</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>写单个 = 系统会自动当成 ==，但建议直接写 ==</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>—— 以下写法只用于 ③ 量表-清单 的「触发条件」列 ——</v>
+        <v>自定义变量</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>直接写变量名</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>情绪均分 &gt;= 4</v>
       </c>
       <c r="D15" t="str">
-        <v>引用该教师最近一次某张量表的结果，判断这张量表现在要不要做</v>
+        <v>变量在 ⑤b 里定义</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>某量表的总分</v>
+        <v/>
       </c>
       <c r="B16" t="str">
-        <v>量表[量表编码].总分</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>取该教师最近一次作答</v>
+        <v>注意：条件里不支持加减乘除。需要算差值、比值，请在 ⑤b 里定义变量，或拆成两个条件用「且」连接。</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>某量表的均分</v>
+        <v/>
       </c>
       <c r="B17" t="str">
-        <v>量表[量表编码].均分</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>量表[SG_FIVE_Q].均分 &gt;= 3.5</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>题数不同的量表之间比较，用均分而不是总分</v>
+        <v>变量名不要包含「且」「或」「总分」「均分」「主导维度」「短板维度」这些关键词，否则会被切坏。</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>某量表的维度分</v>
+        <v/>
       </c>
       <c r="B18" t="str">
-        <v>量表[量表编码].维度[维度编码]</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>量表[SG_FIVE_Q].维度[EMOTION] &gt;= 4</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -1314,91 +1315,147 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>某量表的单题得分</v>
+        <v>—— 以下写法只用于 ③ 量表-清单 的「触发条件」列 ——</v>
       </c>
       <c r="B19" t="str">
-        <v>量表[量表编码].题[题号]</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>量表[SG_FIVE_Q].题[q3] &gt;= 4</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>引用该教师最近一次某张量表的结果，判断这张量表现在要不要做</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>某量表的命中等级</v>
+        <v>某量表的总分</v>
       </c>
       <c r="B20" t="str">
-        <v>量表[量表编码].等级</v>
+        <v>量表[量表编码].总分</v>
       </c>
       <c r="C20" t="str">
-        <v>量表[SG_FIVE_Q].等级 == 'orange'</v>
+        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
       </c>
       <c r="D20" t="str">
-        <v>字符串比较要加引号</v>
+        <v>取该教师最近一次作答</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>某量表的严重度</v>
+        <v>某量表的均分</v>
       </c>
       <c r="B21" t="str">
-        <v>量表[量表编码].严重度</v>
+        <v>量表[量表编码].均分</v>
       </c>
       <c r="C21" t="str">
-        <v>量表[SG_FIVE_Q].严重度 == 'high'</v>
+        <v>量表[SG_FIVE_Q].均分 &gt;= 3.5</v>
       </c>
       <c r="D21" t="str">
-        <v>取值 low/medium/high/crisis</v>
+        <v>题数不同的量表之间比较，用均分而不是总分</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>某量表是否做过</v>
+        <v>某量表的维度分</v>
       </c>
       <c r="B22" t="str">
-        <v>量表[量表编码].已完成</v>
+        <v>量表[量表编码].维度[维度编码]</v>
       </c>
       <c r="C22" t="str">
-        <v>量表[SG_FIVE_Q].已完成 == 1</v>
+        <v>量表[SG_FIVE_Q].维度[EMOTION] &gt;= 4</v>
       </c>
       <c r="D22" t="str">
-        <v>做过为 1，没做过为 0</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>某量表的单题得分</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>量表[量表编码].题[题号]</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>量表[SG_FIVE_Q].题[q3] &gt;= 4</v>
       </c>
       <c r="D23" t="str">
-        <v>引用的量表尚无作答时条件视为「未满足」，该量表标为「当前不需要做」，但不禁止教师手动选。</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>某量表的命中等级</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>量表[量表编码].等级</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>量表[SG_FIVE_Q].等级 == 'orange'</v>
       </c>
       <c r="D24" t="str">
+        <v>字符串比较要加引号</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>某量表的严重度</v>
+      </c>
+      <c r="B25" t="str">
+        <v>量表[量表编码].严重度</v>
+      </c>
+      <c r="C25" t="str">
+        <v>量表[SG_FIVE_Q].严重度 == 'high'</v>
+      </c>
+      <c r="D25" t="str">
+        <v>取值 low/medium/high/crisis</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>某量表是否做过</v>
+      </c>
+      <c r="B26" t="str">
+        <v>量表[量表编码].已完成</v>
+      </c>
+      <c r="C26" t="str">
+        <v>量表[SG_FIVE_Q].已完成 == 1</v>
+      </c>
+      <c r="D26" t="str">
+        <v>做过为 1，没做过为 0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>引用的量表尚无作答时条件视为「未满足」，该量表标为「当前不需要做」，但不禁止教师手动选。</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
         <v>「触发条件」是软推荐，「前置量表编码」才是硬门禁。两者区别见 ① 填写总览。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2870,7 +2927,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_012</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>互动模式 = A型</v>
@@ -2900,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2916,7 +2973,7 @@
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="30.83203125" customWidth="1"/>
+    <col min="15" max="15" width="46.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3010,19 +3067,66 @@
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>学生或教师在任意对话中表达自杀意念，任一命中即走危机流程</v>
+        <v>危机关键词直接走危机流程，不关联量表和工具——这两列留空是对的</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>KW_R02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>心累；撑不住</v>
+      </c>
+      <c r="C3" t="str">
+        <v>身心俱疲；喘不过气；快扛不住了</v>
+      </c>
+      <c r="D3" t="str">
+        <v>累了想睡觉</v>
+      </c>
+      <c r="E3" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F3" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H3" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I3" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="J3" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="K3" t="str">
+        <v>SG_RX_001</v>
+      </c>
+      <c r="L3" t="str">
+        <v>教师自述状态时</v>
+      </c>
+      <c r="M3" t="str">
+        <v>0.85</v>
+      </c>
+      <c r="N3" t="str">
+        <v>always</v>
+      </c>
+      <c r="O3" t="str">
+        <v>常规路由：命中后引导教师做 ③ 里的量表，并预推 ⑦ 里的工具。这两列填的编码必须已存在</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -3081,30 +3185,2395 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_SG_DEFAULT_SUMMARY</v>
+        <v>TPL_SG_ORANGE_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>none</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
+        <v>评估显示您当前处于需要主动支持的区间，主导因素是「${主要归因}」，「${次要归因}」同时在起作用。建议本周内安排一次减负动作，不要等状态继续下滑。</v>
+      </c>
+      <c r="F3" t="str">
+        <v>同上。⑤e 能判出的每个等级都应有一套，否则命中时只能退回兜底文案</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TPL_SG_YELLOW_SUMMARY</v>
+      </c>
+      <c r="B4" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C4" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="D4" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E4" t="str">
+        <v>评估显示您有需要关注的信号，主要集中在「${主要归因}」。目前尚可自主调节，建议先从推荐工具里选一项本周试用并记录效果。</v>
+      </c>
+      <c r="F4" t="str">
+        <v>同上</v>
+      </c>
+      <c r="G4" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TPL_SG_DEFAULT_SUMMARY</v>
+      </c>
+      <c r="B5" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C5" t="str">
+        <v>none</v>
+      </c>
+      <c r="D5" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E5" t="str">
         <v>本次评估未发现需要重点干预的信号，当前状态相对平稳。建议保持现有节奏。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F5" t="str">
         <v>兜底模板：每个模块必须有一条，否则命中未覆盖等级时方案文案会空缺</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G5" t="str">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G101"/>
+  <cols>
+    <col min="1" max="1" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>全链路推演算例 —— 用本模板 ③~⑩ 的示例数据，走一遍完整计算</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>这张表不进系统，是给业务看的。所有数字由真实引擎现算，引擎改了重出模板就会同步更新。</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>对照它可以回答一个问题：我填的这些格子，最后是怎么变成班主任看到的那份方案的。</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>【第 0 步】输入：一位班主任的作答</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>题号</v>
+      </c>
+      <c r="B7" t="str">
+        <v>题干</v>
+      </c>
+      <c r="C7" t="str">
+        <v>教师选了</v>
+      </c>
+      <c r="D7" t="str">
+        <v>原始分</v>
+      </c>
+      <c r="E7" t="str">
+        <v>反向计分</v>
+      </c>
+      <c r="F7" t="str">
+        <v>来源</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>q1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
+      </c>
+      <c r="C8" t="str">
+        <v>经常</v>
+      </c>
+      <c r="D8" t="str">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>否</v>
+      </c>
+      <c r="F8" t="str">
+        <v>④ 量表-题目 / ④b 选项组</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>q2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>这一周，我有多少次感到「什么都是我的责任」？</v>
+      </c>
+      <c r="C9" t="str">
+        <v>经常</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4</v>
+      </c>
+      <c r="E9" t="str">
+        <v>否</v>
+      </c>
+      <c r="F9" t="str">
+        <v>④ 量表-题目 / ④b 选项组</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>q3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
+      </c>
+      <c r="C10" t="str">
+        <v>经常</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>是</v>
+      </c>
+      <c r="F10" t="str">
+        <v>④ 量表-题目 / ④b 选项组</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>q4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
+      </c>
+      <c r="C11" t="str">
+        <v>经常</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4</v>
+      </c>
+      <c r="E11" t="str">
+        <v>是</v>
+      </c>
+      <c r="F11" t="str">
+        <v>④ 量表-题目 / ④b 选项组</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>q5</v>
+      </c>
+      <c r="B12" t="str">
+        <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
+      </c>
+      <c r="C12" t="str">
+        <v>有时</v>
+      </c>
+      <c r="D12" t="str">
+        <v>3</v>
+      </c>
+      <c r="E12" t="str">
+        <v>否</v>
+      </c>
+      <c r="F12" t="str">
+        <v>④ 量表-题目 / ④b 选项组</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>【第 1 步】计分：反向题按「最小值＋最大值−原始分」折算</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>题号</v>
+      </c>
+      <c r="B15" t="str">
+        <v>原始分</v>
+      </c>
+      <c r="C15" t="str">
+        <v>反向</v>
+      </c>
+      <c r="D15" t="str">
+        <v>折算公式</v>
+      </c>
+      <c r="E15" t="str">
+        <v>计分后</v>
+      </c>
+      <c r="F15" t="str">
+        <v>说明</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>q1</v>
+      </c>
+      <c r="B16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" t="str">
+        <v>否</v>
+      </c>
+      <c r="D16" t="str">
+        <v>（不折算）</v>
+      </c>
+      <c r="E16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>q2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>否</v>
+      </c>
+      <c r="D17" t="str">
+        <v>（不折算）</v>
+      </c>
+      <c r="E17" t="str">
+        <v>4</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>q3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>是</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1 + 5 − 4</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>状态越好分越高的题，折算后统一变成「分越高越需要关注」</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>q4</v>
+      </c>
+      <c r="B19" t="str">
+        <v>4</v>
+      </c>
+      <c r="C19" t="str">
+        <v>是</v>
+      </c>
+      <c r="D19" t="str">
+        <v>1 + 5 − 4</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>状态越好分越高的题，折算后统一变成「分越高越需要关注」</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>q5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>否</v>
+      </c>
+      <c r="D20" t="str">
+        <v>（不折算）</v>
+      </c>
+      <c r="E20" t="str">
+        <v>3</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>总分 =</v>
+      </c>
+      <c r="E21" t="str">
+        <v>15</v>
+      </c>
+      <c r="F21" t="str">
+        <v>⑤e 里写「总分」取的就是这个值，不是原始作答之和</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>【第 2 步】维度得分（④c 的「所属题号列表」+「计算方式」）</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>维度编码</v>
+      </c>
+      <c r="B24" t="str">
+        <v>维度名称</v>
+      </c>
+      <c r="C24" t="str">
+        <v>所属题号</v>
+      </c>
+      <c r="D24" t="str">
+        <v>计算方式</v>
+      </c>
+      <c r="E24" t="str">
+        <v>得分</v>
+      </c>
+      <c r="F24" t="str">
+        <v>来源</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>EMOTION</v>
+      </c>
+      <c r="B25" t="str">
+        <v>情绪状态</v>
+      </c>
+      <c r="C25" t="str">
+        <v>q1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>mean</v>
+      </c>
+      <c r="E25" t="str">
+        <v>4</v>
+      </c>
+      <c r="F25" t="str">
+        <v>④c 量表-维度定义</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>BOUNDARY</v>
+      </c>
+      <c r="B26" t="str">
+        <v>角色边界</v>
+      </c>
+      <c r="C26" t="str">
+        <v>q2</v>
+      </c>
+      <c r="D26" t="str">
+        <v>mean</v>
+      </c>
+      <c r="E26" t="str">
+        <v>4</v>
+      </c>
+      <c r="F26" t="str">
+        <v>④c 量表-维度定义</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>MEANING</v>
+      </c>
+      <c r="B27" t="str">
+        <v>意义感知</v>
+      </c>
+      <c r="C27" t="str">
+        <v>q3</v>
+      </c>
+      <c r="D27" t="str">
+        <v>mean</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>④c 量表-维度定义</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>EFFICACY</v>
+      </c>
+      <c r="B28" t="str">
+        <v>效能信心</v>
+      </c>
+      <c r="C28" t="str">
+        <v>q4</v>
+      </c>
+      <c r="D28" t="str">
+        <v>mean</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>④c 量表-维度定义</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SUPPORT</v>
+      </c>
+      <c r="B29" t="str">
+        <v>同伴支持</v>
+      </c>
+      <c r="C29" t="str">
+        <v>q5</v>
+      </c>
+      <c r="D29" t="str">
+        <v>mean</v>
+      </c>
+      <c r="E29" t="str">
+        <v>3</v>
+      </c>
+      <c r="F29" t="str">
+        <v>④c 量表-维度定义</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>【第 3 步】计算变量（⑤b）</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>变量名</v>
+      </c>
+      <c r="B32" t="str">
+        <v>表达式</v>
+      </c>
+      <c r="C32" t="str">
+        <v>算出的值</v>
+      </c>
+      <c r="D32" t="str">
+        <v>说明</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>情绪均分</v>
+      </c>
+      <c r="B33" t="str">
+        <v>维度[EMOTION]</v>
+      </c>
+      <c r="C33" t="str">
+        <v>4</v>
+      </c>
+      <c r="D33" t="str">
+        <v>算不出不会中断评估，只是引用它的规则不会命中</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>连续低意义感次数</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ctx_previousConsecutiveLowMeaning</v>
+      </c>
+      <c r="C34" t="str">
+        <v>0</v>
+      </c>
+      <c r="D34" t="str">
+        <v>算不出不会中断评估，只是引用它的规则不会命中</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>【第 4 步】证据命中判定（⑤d，按「依据量表编码」只取本量表的）</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>证据编码</v>
+      </c>
+      <c r="B37" t="str">
+        <v>归因编码</v>
+      </c>
+      <c r="C37" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="D37" t="str">
+        <v>是否命中</v>
+      </c>
+      <c r="E37" t="str">
+        <v>证据权重</v>
+      </c>
+      <c r="F37" t="str">
+        <v>说明</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SG_EV_001</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SG_AT_EMOTION_EXHAUST</v>
+      </c>
+      <c r="C38" t="str">
+        <v>维度[EMOTION] &gt;= 4</v>
+      </c>
+      <c r="D38" t="str">
+        <v>✓ 命中</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2</v>
+      </c>
+      <c r="F38" t="str">
+        <v>情绪维度得分处于高位，提示情绪资源已被大量消耗</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SG_EV_002</v>
+      </c>
+      <c r="B39" t="str">
+        <v>SG_AT_EMOTION_EXHAUST</v>
+      </c>
+      <c r="C39" t="str">
+        <v>题[q1] &gt;= 4 且 题[q3] &lt;= 2</v>
+      </c>
+      <c r="D39" t="str">
+        <v>✓ 命中</v>
+      </c>
+      <c r="E39" t="str">
+        <v>3</v>
+      </c>
+      <c r="F39" t="str">
+        <v>疲惫与意义感同时告急，是情绪耗竭的核心信号</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SG_EV_003</v>
+      </c>
+      <c r="B40" t="str">
+        <v>SG_AT_BOUNDARY_LOSS</v>
+      </c>
+      <c r="C40" t="str">
+        <v>题[q2] &gt;= 4</v>
+      </c>
+      <c r="D40" t="str">
+        <v>✓ 命中</v>
+      </c>
+      <c r="E40" t="str">
+        <v>2</v>
+      </c>
+      <c r="F40" t="str">
+        <v>频繁出现「什么都是我的责任」的感受</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SG_EV_004</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SG_AT_SUPPORT_MISSING</v>
+      </c>
+      <c r="C41" t="str">
+        <v>题[q5] &gt;= 4</v>
+      </c>
+      <c r="D41" t="str">
+        <v>✗ 未命中</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2</v>
+      </c>
+      <c r="F41" t="str">
+        <v>工作困难长期无人分担</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SG_EV_005</v>
+      </c>
+      <c r="B42" t="str">
+        <v>SG_AT_EMOTION_EXHAUST</v>
+      </c>
+      <c r="C42" t="str">
+        <v>维度[EMOTION] &gt;= 3</v>
+      </c>
+      <c r="D42" t="str">
+        <v>✓ 命中</v>
+      </c>
+      <c r="E42" t="str">
+        <v>1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>情绪维度已高于常模均值，处于早期消耗阶段</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>【第 5 步】归因加权（⑤c 的权重基数 × Σ命中证据权重 → 归一化占比）</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>归因编码</v>
+      </c>
+      <c r="B45" t="str">
+        <v>归因名称</v>
+      </c>
+      <c r="C45" t="str">
+        <v>权重基数</v>
+      </c>
+      <c r="D45" t="str">
+        <v>命中证据</v>
+      </c>
+      <c r="E45" t="str">
+        <v>原始得分</v>
+      </c>
+      <c r="F45" t="str">
+        <v>占比</v>
+      </c>
+      <c r="G45" t="str">
+        <v>强度</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SG_AT_EMOTION_EXHAUST</v>
+      </c>
+      <c r="B46" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="C46" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="D46" t="str">
+        <v>SG_EV_001、SG_EV_002、SG_EV_005</v>
+      </c>
+      <c r="E46" t="str">
+        <v>7.2</v>
+      </c>
+      <c r="F46" t="str">
+        <v>78.3%</v>
+      </c>
+      <c r="G46" t="str">
+        <v>主要</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SG_AT_BOUNDARY_LOSS</v>
+      </c>
+      <c r="B47" t="str">
+        <v>角色边界失守</v>
+      </c>
+      <c r="C47" t="str">
+        <v>1</v>
+      </c>
+      <c r="D47" t="str">
+        <v>SG_EV_003</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2</v>
+      </c>
+      <c r="F47" t="str">
+        <v>21.7%</v>
+      </c>
+      <c r="G47" t="str">
+        <v>次要</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>占比 = 本归因得分 ÷ 所有命中归因得分之和</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>按占比降序取前 3 条；班主任只看到「主要/次要」分组，看不到百分比</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>【第 6 步】分级（⑤e，按优先级从小到大，第一条命中就停）</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>规则编码</v>
+      </c>
+      <c r="B52" t="str">
+        <v>优先级</v>
+      </c>
+      <c r="C52" t="str">
+        <v>依据量表</v>
+      </c>
+      <c r="D52" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="E52" t="str">
+        <v>是否命中</v>
+      </c>
+      <c r="F52" t="str">
+        <v>判出等级</v>
+      </c>
+      <c r="G52" t="str">
+        <v>严重度</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SG_GRADE_RED</v>
+      </c>
+      <c r="B53" t="str">
+        <v>10</v>
+      </c>
+      <c r="C53" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D53" t="str">
+        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+      </c>
+      <c r="E53" t="str">
+        <v>✗</v>
+      </c>
+      <c r="F53" t="str">
+        <v>red</v>
+      </c>
+      <c r="G53" t="str">
+        <v>crisis</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SG_GRADE_ORANGE</v>
+      </c>
+      <c r="B54" t="str">
+        <v>20</v>
+      </c>
+      <c r="C54" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D54" t="str">
+        <v>总分 &gt;= 17</v>
+      </c>
+      <c r="E54" t="str">
+        <v>✗</v>
+      </c>
+      <c r="F54" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G54" t="str">
+        <v>high</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SG_GRADE_YELLOW</v>
+      </c>
+      <c r="B55" t="str">
+        <v>30</v>
+      </c>
+      <c r="C55" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D55" t="str">
+        <v>总分 &gt;= 12</v>
+      </c>
+      <c r="E55" t="str">
+        <v>✓ 命中并停止</v>
+      </c>
+      <c r="F55" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G55" t="str">
+        <v>medium</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>SG_GRADE_DEFAULT</v>
+      </c>
+      <c r="B56" t="str">
+        <v>999</v>
+      </c>
+      <c r="C56" t="str">
+        <v>（不限定）</v>
+      </c>
+      <c r="D56" t="str">
+        <v>（兜底，无条件）</v>
+      </c>
+      <c r="E56" t="str">
+        <v>✗</v>
+      </c>
+      <c r="F56" t="str">
+        <v>none</v>
+      </c>
+      <c r="G56" t="str">
+        <v>low</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v>最终等级 →</v>
+      </c>
+      <c r="F57" t="str">
+        <v>yellow（需关注）</v>
+      </c>
+      <c r="G57" t="str">
+        <v>medium</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>注意：分级与归因是解耦的——等级由 ⑤e 判，归因由 ⑤c/⑤d 算，两者互不决定</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>【第 7 步】红线检查（⑥）</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>红线条件</v>
+      </c>
+      <c r="B61" t="str">
+        <v>是否命中</v>
+      </c>
+      <c r="C61" t="str">
+        <v>后果</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+      </c>
+      <c r="B62" t="str">
+        <v>✗ 未命中</v>
+      </c>
+      <c r="C62" t="str">
+        <v>未熔断，继续生成方案</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>【第 8 步】工具加权匹配（⑦）：四项加权求和，不是「全都要满足」</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>打分项</v>
+      </c>
+      <c r="B65" t="str">
+        <v>权重</v>
+      </c>
+      <c r="C65" t="str">
+        <v>本次情况</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>对应归因命中（按该归因占比加权）</v>
+      </c>
+      <c r="B66" t="str">
+        <v>×10</v>
+      </c>
+      <c r="C66" t="str">
+        <v>情绪耗竭 78%；角色边界失守 22%</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>工具标签 ∩ 归因的工具标签</v>
+      </c>
+      <c r="B67" t="str">
+        <v>×3</v>
+      </c>
+      <c r="C67" t="str">
+        <v>self_growth、emotion、pressure、boundary</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>严重度相同</v>
+      </c>
+      <c r="B68" t="str">
+        <v>×2</v>
+      </c>
+      <c r="C68" t="str">
+        <v>本次严重度 medium</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>作用维度命中薄弱维度（得分 &lt;= 2.5）</v>
+      </c>
+      <c r="B69" t="str">
+        <v>×2</v>
+      </c>
+      <c r="C69" t="str">
+        <v>意义感知、效能信心</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>工具编码</v>
+      </c>
+      <c r="B71" t="str">
+        <v>工具名称</v>
+      </c>
+      <c r="C71" t="str">
+        <v>对应归因</v>
+      </c>
+      <c r="D71" t="str">
+        <v>严重度</v>
+      </c>
+      <c r="E71" t="str">
+        <v>作用维度</v>
+      </c>
+      <c r="F71" t="str">
+        <v>得分</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SG_RX_001</v>
+      </c>
+      <c r="B72" t="str">
+        <v>三分钟补能法</v>
+      </c>
+      <c r="C72" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="D72" t="str">
+        <v>medium</v>
+      </c>
+      <c r="E72" t="str">
+        <v>情绪状态</v>
+      </c>
+      <c r="F72" t="str">
+        <v>12.83</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v/>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>禁忌规则（⑧）里 type=block 的是唯一硬过滤，命中直接剔除该工具</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v/>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>【第 9 步】输出模板渲染（⑩，按判出的等级取）</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>命中模板</v>
+      </c>
+      <c r="B76" t="str">
+        <v>TPL_SG_YELLOW_SUMMARY</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>模板原文</v>
+      </c>
+      <c r="B77" t="str">
+        <v>评估显示您有需要关注的信号，主要集中在「${主要归因}」。目前尚可自主调节，建议先从推荐工具里选一项本周试用并记录效果。</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>${主要归因}</v>
+      </c>
+      <c r="B78" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>${次要归因}</v>
+      </c>
+      <c r="B79" t="str">
+        <v>角色边界失守</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>渲染结果</v>
+      </c>
+      <c r="B80" t="str">
+        <v>评估显示您有需要关注的信号，主要集中在「情绪耗竭」。目前尚可自主调节，建议先从推荐工具里选一项本周试用并记录效果。</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>【第 10 步】班主任最终看到什么</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>报告等级徽章</v>
+      </c>
+      <c r="B83" t="str">
+        <v>需关注</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>归因构成</v>
+      </c>
+      <c r="B84" t="str">
+        <v>主要 情绪耗竭  |  次要 角色边界失守</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>关键依据</v>
+      </c>
+      <c r="B85" t="str">
+        <v>情绪维度得分处于高位，提示情绪资源已被大量消耗；疲惫与意义感同时告急，是情绪耗竭的核心信号；情绪维度已高于常模均值，处于早期消耗阶段；频繁出现「什么都是我的责任」的感受</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>3 天行动</v>
+      </c>
+      <c r="B86" t="str">
+        <v>针对「情绪耗竭」  |  针对「角色边界失守」</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>工具卡</v>
+      </c>
+      <c r="B87" t="str">
+        <v>三分钟补能法</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>【对照案例：同一套规则，另一位教师触发红线】</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>这位教师的作答</v>
+      </c>
+      <c r="B90" t="str">
+        <v>q1=4  q2=4  q3=2  q4=3  q5=4</v>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>折算后</v>
+      </c>
+      <c r="B91" t="str">
+        <v>q1=4  q2=4  q3=4  q4=3  q5=4</v>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>差别在哪</v>
+      </c>
+      <c r="B92" t="str">
+        <v>q3 原始分从 4 变成 2。q3 是反向题，折算后从 2 变成 4，正好越过红线阈值。</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>红线条件</v>
+      </c>
+      <c r="B93" t="str">
+        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>是否熔断</v>
+      </c>
+      <c r="B94" t="str">
+        <v>✓ 熔断</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>后果</v>
+      </c>
+      <c r="B95" t="str">
+        <v>不生成方案。第 8~10 步全部不发生：教师看到的是安全转介提示，不是评估报告，也没有工具卡和 3 天行动。</v>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>这说明什么</v>
+      </c>
+      <c r="B96" t="str">
+        <v>反向题上「原始分低」＝「状态差」。写 ⑤e/⑥ 的条件时，方向写反不会报错，但红线会打在状态好的人身上、或对真正高危的人永不触发。详见 ⑤a 的「反向题的方向别写反」。</v>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v/>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>【看不到的东西，以及为什么】</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>占比百分比</v>
+      </c>
+      <c r="B99" t="str">
+        <v>占比是规则匹配强度，不是测量精度。直接给百分比会被当成诊断承诺，所以只呈现主要/次要分组。</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>归因编码、维度编码</v>
+      </c>
+      <c r="B100" t="str">
+        <v>面向班主任的文案一律用中文名。编码泄漏到界面上就是事故。</v>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>触发条件原文</v>
+      </c>
+      <c r="B101" t="str">
+        <v>业务的阈值是内部判断依据，不对教师展示。教师只看到「触发条件说明」那一列的人话。</v>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G101"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/templates/三库填写模板_v4.xlsx
+++ b/business-libraries/templates/三库填写模板_v4.xlsx
@@ -2071,7 +2071,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>none</v>
+        <v>green</v>
       </c>
       <c r="G5" t="str">
         <v>状态平稳</v>
@@ -3237,7 +3237,7 @@
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>none</v>
+        <v>green</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
@@ -4530,7 +4530,7 @@
         <v>✗</v>
       </c>
       <c r="F56" t="str">
-        <v>none</v>
+        <v>green</v>
       </c>
       <c r="G56" t="str">
         <v>low</v>
@@ -5580,7 +5580,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -5831,10 +5831,10 @@
         <v>风险等级</v>
       </c>
       <c r="B18" t="str">
-        <v>none</v>
+        <v>blue</v>
       </c>
       <c r="C18" t="str">
-        <v>无风险标记</v>
+        <v>蓝·持续观察</v>
       </c>
       <c r="D18" t="str">
         <v>同上</v>
@@ -5842,16 +5842,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>适用学部</v>
+        <v>风险等级</v>
       </c>
       <c r="B19" t="str">
-        <v>all</v>
+        <v>green</v>
       </c>
       <c r="C19" t="str">
-        <v>全学部</v>
+        <v>绿·正常（兜底）</v>
       </c>
       <c r="D19" t="str">
-        <v>量表-清单 / 工具-处方总表</v>
+        <v>同上</v>
       </c>
     </row>
     <row r="20">
@@ -5859,13 +5859,13 @@
         <v>适用学部</v>
       </c>
       <c r="B20" t="str">
-        <v>primary</v>
+        <v>all</v>
       </c>
       <c r="C20" t="str">
-        <v>小学部</v>
+        <v>全学部</v>
       </c>
       <c r="D20" t="str">
-        <v>同上</v>
+        <v>量表-清单 / 工具-处方总表</v>
       </c>
     </row>
     <row r="21">
@@ -5873,10 +5873,10 @@
         <v>适用学部</v>
       </c>
       <c r="B21" t="str">
-        <v>junior</v>
+        <v>primary</v>
       </c>
       <c r="C21" t="str">
-        <v>初中部</v>
+        <v>小学部</v>
       </c>
       <c r="D21" t="str">
         <v>同上</v>
@@ -5887,10 +5887,10 @@
         <v>适用学部</v>
       </c>
       <c r="B22" t="str">
-        <v>senior</v>
+        <v>junior</v>
       </c>
       <c r="C22" t="str">
-        <v>高中部</v>
+        <v>初中部</v>
       </c>
       <c r="D22" t="str">
         <v>同上</v>
@@ -5901,10 +5901,10 @@
         <v>适用学部</v>
       </c>
       <c r="B23" t="str">
-        <v>repeat</v>
+        <v>senior</v>
       </c>
       <c r="C23" t="str">
-        <v>复读部</v>
+        <v>高中部</v>
       </c>
       <c r="D23" t="str">
         <v>同上</v>
@@ -5912,16 +5912,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>施测/适用对象</v>
+        <v>适用学部</v>
       </c>
       <c r="B24" t="str">
-        <v>teacher</v>
+        <v>repeat</v>
       </c>
       <c r="C24" t="str">
-        <v>班主任本人</v>
+        <v>复读部</v>
       </c>
       <c r="D24" t="str">
-        <v>量表-清单 / 工具-处方总表</v>
+        <v>同上</v>
       </c>
     </row>
     <row r="25">
@@ -5929,13 +5929,13 @@
         <v>施测/适用对象</v>
       </c>
       <c r="B25" t="str">
-        <v>student</v>
+        <v>teacher</v>
       </c>
       <c r="C25" t="str">
-        <v>学生</v>
+        <v>班主任本人</v>
       </c>
       <c r="D25" t="str">
-        <v>同上</v>
+        <v>量表-清单 / 工具-处方总表</v>
       </c>
     </row>
     <row r="26">
@@ -5943,10 +5943,10 @@
         <v>施测/适用对象</v>
       </c>
       <c r="B26" t="str">
-        <v>guardian</v>
+        <v>student</v>
       </c>
       <c r="C26" t="str">
-        <v>家长</v>
+        <v>学生</v>
       </c>
       <c r="D26" t="str">
         <v>同上</v>
@@ -5957,10 +5957,10 @@
         <v>施测/适用对象</v>
       </c>
       <c r="B27" t="str">
-        <v>class</v>
+        <v>guardian</v>
       </c>
       <c r="C27" t="str">
-        <v>班级整体</v>
+        <v>家长</v>
       </c>
       <c r="D27" t="str">
         <v>同上</v>
@@ -5968,16 +5968,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>数据敏感级</v>
+        <v>施测/适用对象</v>
       </c>
       <c r="B28" t="str">
-        <v>internal</v>
+        <v>class</v>
       </c>
       <c r="C28" t="str">
-        <v>内部限阅</v>
+        <v>班级整体</v>
       </c>
       <c r="D28" t="str">
-        <v>量表-清单</v>
+        <v>同上</v>
       </c>
     </row>
     <row r="29">
@@ -5985,10 +5985,10 @@
         <v>数据敏感级</v>
       </c>
       <c r="B29" t="str">
-        <v>sensitive</v>
+        <v>internal</v>
       </c>
       <c r="C29" t="str">
-        <v>敏感</v>
+        <v>内部限阅</v>
       </c>
       <c r="D29" t="str">
         <v>量表-清单</v>
@@ -5999,10 +5999,10 @@
         <v>数据敏感级</v>
       </c>
       <c r="B30" t="str">
-        <v>highly_sensitive</v>
+        <v>sensitive</v>
       </c>
       <c r="C30" t="str">
-        <v>高度敏感</v>
+        <v>敏感</v>
       </c>
       <c r="D30" t="str">
         <v>量表-清单</v>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>来源属性</v>
+        <v>数据敏感级</v>
       </c>
       <c r="B31" t="str">
-        <v>proprietary</v>
+        <v>highly_sensitive</v>
       </c>
       <c r="C31" t="str">
-        <v>六力自有</v>
+        <v>高度敏感</v>
       </c>
       <c r="D31" t="str">
         <v>量表-清单</v>
@@ -6027,10 +6027,10 @@
         <v>来源属性</v>
       </c>
       <c r="B32" t="str">
-        <v>external</v>
+        <v>proprietary</v>
       </c>
       <c r="C32" t="str">
-        <v>外部量表·需授权</v>
+        <v>六力自有</v>
       </c>
       <c r="D32" t="str">
         <v>量表-清单</v>
@@ -6041,10 +6041,10 @@
         <v>来源属性</v>
       </c>
       <c r="B33" t="str">
-        <v>adapted</v>
+        <v>external</v>
       </c>
       <c r="C33" t="str">
-        <v>改编自外部</v>
+        <v>外部量表·需授权</v>
       </c>
       <c r="D33" t="str">
         <v>量表-清单</v>
@@ -6052,13 +6052,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>触发方式</v>
+        <v>来源属性</v>
       </c>
       <c r="B34" t="str">
-        <v>manual</v>
+        <v>adapted</v>
       </c>
       <c r="C34" t="str">
-        <v>教师手动发起</v>
+        <v>改编自外部</v>
       </c>
       <c r="D34" t="str">
         <v>量表-清单</v>
@@ -6069,10 +6069,10 @@
         <v>触发方式</v>
       </c>
       <c r="B35" t="str">
-        <v>auto</v>
+        <v>manual</v>
       </c>
       <c r="C35" t="str">
-        <v>系统自动推荐</v>
+        <v>教师手动发起</v>
       </c>
       <c r="D35" t="str">
         <v>量表-清单</v>
@@ -6083,10 +6083,10 @@
         <v>触发方式</v>
       </c>
       <c r="B36" t="str">
-        <v>scheduled</v>
+        <v>auto</v>
       </c>
       <c r="C36" t="str">
-        <v>定时推送</v>
+        <v>系统自动推荐</v>
       </c>
       <c r="D36" t="str">
         <v>量表-清单</v>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>作答频次</v>
+        <v>触发方式</v>
       </c>
       <c r="B37" t="str">
-        <v>once</v>
+        <v>scheduled</v>
       </c>
       <c r="C37" t="str">
-        <v>仅一次</v>
+        <v>定时推送</v>
       </c>
       <c r="D37" t="str">
         <v>量表-清单</v>
@@ -6111,10 +6111,10 @@
         <v>作答频次</v>
       </c>
       <c r="B38" t="str">
-        <v>daily</v>
+        <v>once</v>
       </c>
       <c r="C38" t="str">
-        <v>每天</v>
+        <v>仅一次</v>
       </c>
       <c r="D38" t="str">
         <v>量表-清单</v>
@@ -6125,10 +6125,10 @@
         <v>作答频次</v>
       </c>
       <c r="B39" t="str">
-        <v>weekly</v>
+        <v>daily</v>
       </c>
       <c r="C39" t="str">
-        <v>每周</v>
+        <v>每天</v>
       </c>
       <c r="D39" t="str">
         <v>量表-清单</v>
@@ -6139,10 +6139,10 @@
         <v>作答频次</v>
       </c>
       <c r="B40" t="str">
-        <v>monthly</v>
+        <v>weekly</v>
       </c>
       <c r="C40" t="str">
-        <v>每月</v>
+        <v>每周</v>
       </c>
       <c r="D40" t="str">
         <v>量表-清单</v>
@@ -6153,10 +6153,10 @@
         <v>作答频次</v>
       </c>
       <c r="B41" t="str">
-        <v>per_case</v>
+        <v>monthly</v>
       </c>
       <c r="C41" t="str">
-        <v>每个个案</v>
+        <v>每月</v>
       </c>
       <c r="D41" t="str">
         <v>量表-清单</v>
@@ -6164,13 +6164,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>结果可见性</v>
+        <v>作答频次</v>
       </c>
       <c r="B42" t="str">
-        <v>teacher_only</v>
+        <v>per_case</v>
       </c>
       <c r="C42" t="str">
-        <v>仅教师可见</v>
+        <v>每个个案</v>
       </c>
       <c r="D42" t="str">
         <v>量表-清单</v>
@@ -6181,10 +6181,10 @@
         <v>结果可见性</v>
       </c>
       <c r="B43" t="str">
-        <v>teacher_and_student</v>
+        <v>teacher_only</v>
       </c>
       <c r="C43" t="str">
-        <v>教师和学生可见</v>
+        <v>仅教师可见</v>
       </c>
       <c r="D43" t="str">
         <v>量表-清单</v>
@@ -6195,10 +6195,10 @@
         <v>结果可见性</v>
       </c>
       <c r="B44" t="str">
-        <v>psychologist</v>
+        <v>teacher_and_student</v>
       </c>
       <c r="C44" t="str">
-        <v>心理专员可见</v>
+        <v>教师和学生可见</v>
       </c>
       <c r="D44" t="str">
         <v>量表-清单</v>
@@ -6206,13 +6206,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>施测形式</v>
+        <v>结果可见性</v>
       </c>
       <c r="B45" t="str">
-        <v>self_report</v>
+        <v>psychologist</v>
       </c>
       <c r="C45" t="str">
-        <v>自评问卷</v>
+        <v>心理专员可见</v>
       </c>
       <c r="D45" t="str">
         <v>量表-清单</v>
@@ -6223,10 +6223,10 @@
         <v>施测形式</v>
       </c>
       <c r="B46" t="str">
-        <v>observation</v>
+        <v>self_report</v>
       </c>
       <c r="C46" t="str">
-        <v>观察记录</v>
+        <v>自评问卷</v>
       </c>
       <c r="D46" t="str">
         <v>量表-清单</v>
@@ -6237,10 +6237,10 @@
         <v>施测形式</v>
       </c>
       <c r="B47" t="str">
-        <v>interview</v>
+        <v>observation</v>
       </c>
       <c r="C47" t="str">
-        <v>访谈提纲</v>
+        <v>观察记录</v>
       </c>
       <c r="D47" t="str">
         <v>量表-清单</v>
@@ -6251,10 +6251,10 @@
         <v>施测形式</v>
       </c>
       <c r="B48" t="str">
-        <v>checklist</v>
+        <v>interview</v>
       </c>
       <c r="C48" t="str">
-        <v>核查清单</v>
+        <v>访谈提纲</v>
       </c>
       <c r="D48" t="str">
         <v>量表-清单</v>
@@ -6262,16 +6262,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>题型</v>
+        <v>施测形式</v>
       </c>
       <c r="B49" t="str">
-        <v>single</v>
+        <v>checklist</v>
       </c>
       <c r="C49" t="str">
-        <v>单选题</v>
+        <v>核查清单</v>
       </c>
       <c r="D49" t="str">
-        <v>量表-题目</v>
+        <v>量表-清单</v>
       </c>
     </row>
     <row r="50">
@@ -6279,10 +6279,10 @@
         <v>题型</v>
       </c>
       <c r="B50" t="str">
-        <v>multiple</v>
+        <v>single</v>
       </c>
       <c r="C50" t="str">
-        <v>多选题</v>
+        <v>单选题</v>
       </c>
       <c r="D50" t="str">
         <v>量表-题目</v>
@@ -6293,10 +6293,10 @@
         <v>题型</v>
       </c>
       <c r="B51" t="str">
-        <v>text</v>
+        <v>multiple</v>
       </c>
       <c r="C51" t="str">
-        <v>文本填空</v>
+        <v>多选题</v>
       </c>
       <c r="D51" t="str">
         <v>量表-题目</v>
@@ -6307,10 +6307,10 @@
         <v>题型</v>
       </c>
       <c r="B52" t="str">
-        <v>matrix</v>
+        <v>text</v>
       </c>
       <c r="C52" t="str">
-        <v>矩阵题</v>
+        <v>文本填空</v>
       </c>
       <c r="D52" t="str">
         <v>量表-题目</v>
@@ -6318,13 +6318,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>数据用途</v>
+        <v>题型</v>
       </c>
       <c r="B53" t="str">
-        <v>compute</v>
+        <v>matrix</v>
       </c>
       <c r="C53" t="str">
-        <v>计算维度分</v>
+        <v>矩阵题</v>
       </c>
       <c r="D53" t="str">
         <v>量表-题目</v>
@@ -6335,10 +6335,10 @@
         <v>数据用途</v>
       </c>
       <c r="B54" t="str">
-        <v>monitor</v>
+        <v>compute</v>
       </c>
       <c r="C54" t="str">
-        <v>质量监测</v>
+        <v>计算维度分</v>
       </c>
       <c r="D54" t="str">
         <v>量表-题目</v>
@@ -6349,10 +6349,10 @@
         <v>数据用途</v>
       </c>
       <c r="B55" t="str">
-        <v>aux</v>
+        <v>monitor</v>
       </c>
       <c r="C55" t="str">
-        <v>辅助信息</v>
+        <v>质量监测</v>
       </c>
       <c r="D55" t="str">
         <v>量表-题目</v>
@@ -6360,16 +6360,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>计算方式</v>
+        <v>数据用途</v>
       </c>
       <c r="B56" t="str">
-        <v>mean</v>
+        <v>aux</v>
       </c>
       <c r="C56" t="str">
-        <v>维度内各题均值</v>
+        <v>辅助信息</v>
       </c>
       <c r="D56" t="str">
-        <v>量表-维度定义</v>
+        <v>量表-题目</v>
       </c>
     </row>
     <row r="57">
@@ -6377,10 +6377,10 @@
         <v>计算方式</v>
       </c>
       <c r="B57" t="str">
-        <v>sum</v>
+        <v>mean</v>
       </c>
       <c r="C57" t="str">
-        <v>维度内各题总分</v>
+        <v>维度内各题均值</v>
       </c>
       <c r="D57" t="str">
         <v>量表-维度定义</v>
@@ -6391,10 +6391,10 @@
         <v>计算方式</v>
       </c>
       <c r="B58" t="str">
-        <v>weighted</v>
+        <v>sum</v>
       </c>
       <c r="C58" t="str">
-        <v>维度内各题加权求和</v>
+        <v>维度内各题总分</v>
       </c>
       <c r="D58" t="str">
         <v>量表-维度定义</v>
@@ -6402,16 +6402,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>工具形式</v>
+        <v>计算方式</v>
       </c>
       <c r="B59" t="str">
-        <v>exercise</v>
+        <v>weighted</v>
       </c>
       <c r="C59" t="str">
-        <v>练习</v>
+        <v>维度内各题加权求和</v>
       </c>
       <c r="D59" t="str">
-        <v>工具-处方总表</v>
+        <v>量表-维度定义</v>
       </c>
     </row>
     <row r="60">
@@ -6419,10 +6419,10 @@
         <v>工具形式</v>
       </c>
       <c r="B60" t="str">
-        <v>script</v>
+        <v>exercise</v>
       </c>
       <c r="C60" t="str">
-        <v>话术</v>
+        <v>练习</v>
       </c>
       <c r="D60" t="str">
         <v>工具-处方总表</v>
@@ -6433,10 +6433,10 @@
         <v>工具形式</v>
       </c>
       <c r="B61" t="str">
-        <v>checklist</v>
+        <v>script</v>
       </c>
       <c r="C61" t="str">
-        <v>清单</v>
+        <v>话术</v>
       </c>
       <c r="D61" t="str">
         <v>工具-处方总表</v>
@@ -6447,10 +6447,10 @@
         <v>工具形式</v>
       </c>
       <c r="B62" t="str">
-        <v>framework</v>
+        <v>checklist</v>
       </c>
       <c r="C62" t="str">
-        <v>框架</v>
+        <v>清单</v>
       </c>
       <c r="D62" t="str">
         <v>工具-处方总表</v>
@@ -6461,10 +6461,10 @@
         <v>工具形式</v>
       </c>
       <c r="B63" t="str">
-        <v>worksheet</v>
+        <v>framework</v>
       </c>
       <c r="C63" t="str">
-        <v>工作表</v>
+        <v>框架</v>
       </c>
       <c r="D63" t="str">
         <v>工具-处方总表</v>
@@ -6472,13 +6472,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>证据等级</v>
+        <v>工具形式</v>
       </c>
       <c r="B64" t="str">
-        <v>A</v>
+        <v>worksheet</v>
       </c>
       <c r="C64" t="str">
-        <v>随机对照试验支持</v>
+        <v>工作表</v>
       </c>
       <c r="D64" t="str">
         <v>工具-处方总表</v>
@@ -6489,10 +6489,10 @@
         <v>证据等级</v>
       </c>
       <c r="B65" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="C65" t="str">
-        <v>准实验或队列研究支持</v>
+        <v>随机对照试验支持</v>
       </c>
       <c r="D65" t="str">
         <v>工具-处方总表</v>
@@ -6503,10 +6503,10 @@
         <v>证据等级</v>
       </c>
       <c r="B66" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="C66" t="str">
-        <v>专家共识或案例报告</v>
+        <v>准实验或队列研究支持</v>
       </c>
       <c r="D66" t="str">
         <v>工具-处方总表</v>
@@ -6517,10 +6517,10 @@
         <v>证据等级</v>
       </c>
       <c r="B67" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="C67" t="str">
-        <v>理论推导或经验总结</v>
+        <v>专家共识或案例报告</v>
       </c>
       <c r="D67" t="str">
         <v>工具-处方总表</v>
@@ -6528,16 +6528,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>禁忌类型</v>
+        <v>证据等级</v>
       </c>
       <c r="B68" t="str">
-        <v>block</v>
+        <v>D</v>
       </c>
       <c r="C68" t="str">
-        <v>硬禁忌（直接排除该工具）</v>
+        <v>理论推导或经验总结</v>
       </c>
       <c r="D68" t="str">
-        <v>工具-禁忌规则</v>
+        <v>工具-处方总表</v>
       </c>
     </row>
     <row r="69">
@@ -6545,10 +6545,10 @@
         <v>禁忌类型</v>
       </c>
       <c r="B69" t="str">
-        <v>warn</v>
+        <v>block</v>
       </c>
       <c r="C69" t="str">
-        <v>软禁忌（提醒但不排除）</v>
+        <v>硬禁忌（直接排除该工具）</v>
       </c>
       <c r="D69" t="str">
         <v>工具-禁忌规则</v>
@@ -6556,16 +6556,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>匹配模式</v>
+        <v>禁忌类型</v>
       </c>
       <c r="B70" t="str">
-        <v>exact</v>
+        <v>warn</v>
       </c>
       <c r="C70" t="str">
-        <v>精确匹配</v>
+        <v>软禁忌（提醒但不排除）</v>
       </c>
       <c r="D70" t="str">
-        <v>关键词-路由</v>
+        <v>工具-禁忌规则</v>
       </c>
     </row>
     <row r="71">
@@ -6573,10 +6573,10 @@
         <v>匹配模式</v>
       </c>
       <c r="B71" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="C71" t="str">
-        <v>模糊匹配</v>
+        <v>精确匹配</v>
       </c>
       <c r="D71" t="str">
         <v>关键词-路由</v>
@@ -6587,10 +6587,10 @@
         <v>匹配模式</v>
       </c>
       <c r="B72" t="str">
-        <v>regex</v>
+        <v>fuzzy</v>
       </c>
       <c r="C72" t="str">
-        <v>正则表达式</v>
+        <v>模糊匹配</v>
       </c>
       <c r="D72" t="str">
         <v>关键词-路由</v>
@@ -6598,16 +6598,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>熔断范围</v>
+        <v>匹配模式</v>
       </c>
       <c r="B73" t="str">
-        <v>instrument</v>
+        <v>regex</v>
       </c>
       <c r="C73" t="str">
-        <v>仅当前量表</v>
+        <v>正则表达式</v>
       </c>
       <c r="D73" t="str">
-        <v>归因-红线熔断</v>
+        <v>关键词-路由</v>
       </c>
     </row>
     <row r="74">
@@ -6615,10 +6615,10 @@
         <v>熔断范围</v>
       </c>
       <c r="B74" t="str">
-        <v>module</v>
+        <v>instrument</v>
       </c>
       <c r="C74" t="str">
-        <v>整个模块</v>
+        <v>仅当前量表</v>
       </c>
       <c r="D74" t="str">
         <v>归因-红线熔断</v>
@@ -6629,10 +6629,10 @@
         <v>熔断范围</v>
       </c>
       <c r="B75" t="str">
-        <v>system</v>
+        <v>module</v>
       </c>
       <c r="C75" t="str">
-        <v>全系统</v>
+        <v>整个模块</v>
       </c>
       <c r="D75" t="str">
         <v>归因-红线熔断</v>
@@ -6640,16 +6640,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>模板类型</v>
+        <v>熔断范围</v>
       </c>
       <c r="B76" t="str">
-        <v>summary</v>
+        <v>system</v>
       </c>
       <c r="C76" t="str">
-        <v>问题摘要</v>
+        <v>全系统</v>
       </c>
       <c r="D76" t="str">
-        <v>方案输出模板</v>
+        <v>归因-红线熔断</v>
       </c>
     </row>
     <row r="77">
@@ -6657,10 +6657,10 @@
         <v>模板类型</v>
       </c>
       <c r="B77" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="C77" t="str">
-        <v>评估结论</v>
+        <v>问题摘要</v>
       </c>
       <c r="D77" t="str">
         <v>方案输出模板</v>
@@ -6671,10 +6671,10 @@
         <v>模板类型</v>
       </c>
       <c r="B78" t="str">
-        <v>attribution</v>
+        <v>conclusion</v>
       </c>
       <c r="C78" t="str">
-        <v>归因说明</v>
+        <v>评估结论</v>
       </c>
       <c r="D78" t="str">
         <v>方案输出模板</v>
@@ -6685,10 +6685,10 @@
         <v>模板类型</v>
       </c>
       <c r="B79" t="str">
-        <v>goal</v>
+        <v>attribution</v>
       </c>
       <c r="C79" t="str">
-        <v>支持目标</v>
+        <v>归因说明</v>
       </c>
       <c r="D79" t="str">
         <v>方案输出模板</v>
@@ -6699,10 +6699,10 @@
         <v>模板类型</v>
       </c>
       <c r="B80" t="str">
-        <v>action</v>
+        <v>goal</v>
       </c>
       <c r="C80" t="str">
-        <v>行动项</v>
+        <v>支持目标</v>
       </c>
       <c r="D80" t="str">
         <v>方案输出模板</v>
@@ -6713,10 +6713,10 @@
         <v>模板类型</v>
       </c>
       <c r="B81" t="str">
-        <v>tool</v>
+        <v>action</v>
       </c>
       <c r="C81" t="str">
-        <v>推荐工具</v>
+        <v>行动项</v>
       </c>
       <c r="D81" t="str">
         <v>方案输出模板</v>
@@ -6727,10 +6727,10 @@
         <v>模板类型</v>
       </c>
       <c r="B82" t="str">
-        <v>caution</v>
+        <v>tool</v>
       </c>
       <c r="C82" t="str">
-        <v>注意事项/禁忌</v>
+        <v>推荐工具</v>
       </c>
       <c r="D82" t="str">
         <v>方案输出模板</v>
@@ -6741,18 +6741,32 @@
         <v>模板类型</v>
       </c>
       <c r="B83" t="str">
-        <v>review</v>
+        <v>caution</v>
       </c>
       <c r="C83" t="str">
-        <v>复盘提示</v>
+        <v>注意事项/禁忌</v>
       </c>
       <c r="D83" t="str">
         <v>方案输出模板</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>模板类型</v>
+      </c>
+      <c r="B84" t="str">
+        <v>review</v>
+      </c>
+      <c r="C84" t="str">
+        <v>复盘提示</v>
+      </c>
+      <c r="D84" t="str">
+        <v>方案输出模板</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D84"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/templates/三库填写模板_v4.xlsx
+++ b/business-libraries/templates/三库填写模板_v4.xlsx
@@ -1860,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P5"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1875,7 +1875,9 @@
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="32.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1919,6 +1921,12 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
@@ -1963,6 +1971,12 @@
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>PRD 8.3</v>
       </c>
     </row>
@@ -2007,7 +2021,13 @@
         <v>30天后复评</v>
       </c>
       <c r="N3" t="str">
-        <v>PRD 8.3</v>
+        <v>SG_RX_001</v>
+      </c>
+      <c r="O3" t="str">
+        <v>本周内完成一次一对一沟通并记录反馈。</v>
+      </c>
+      <c r="P3" t="str">
+        <v>PRD 8.3　【示范：干预工具填工具编码（多个用;分隔），干预动作直接进方案】</v>
       </c>
     </row>
     <row r="4">
@@ -2051,6 +2071,12 @@
         <v>90天后复评</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>PRD 8.3</v>
       </c>
     </row>
@@ -2095,12 +2121,18 @@
         <v/>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>PRD 8.3　【兜底：留空触发条件，优先级必须是全表最大】</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
   </ignoredErrors>
 </worksheet>
 </file>
